--- a/docs/Estimativas_UCP.xlsx
+++ b/docs/Estimativas_UCP.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Equipe</t>
   </si>
   <si>
-    <t xml:space="preserve">4 desenvolvedores full stack</t>
+    <t xml:space="preserve">3 desenvolvedores full stack (Max Soares, Lucas Mendes, Lorenzo Oliveira)</t>
   </si>
   <si>
     <t xml:space="preserve">Sprints planejadas</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Esforço por desenvolvedor (horas)</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribuído entre os 4 devs.</t>
+    <t xml:space="preserve">Distribuído entre os 3 devs.</t>
   </si>
   <si>
     <t xml:space="preserve">Carga semanal por desenvolvedor</t>
@@ -678,7 +678,7 @@
     <t xml:space="preserve">• A distribuição inicial reserva 5% para Sprint 1 (planejamento), com pico de 30% nas sprints 2 e 3.</t>
   </si>
   <si>
-    <t xml:space="preserve">• As horas por dev consideram divisão igualitária entre os 4 membros da equipe.</t>
+    <t xml:space="preserve">• As horas por dev consideram divisão igualitária entre os 3 membros da equipe.</t>
   </si>
   <si>
     <t xml:space="preserve">• Recalibre os percentuais a cada retrospectiva, comparando estimado x real.</t>
@@ -885,164 +885,160 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1301,271 +1297,271 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <f aca="false">'Atores (UAW)'!E10</f>
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <f aca="false">'Casos de Uso (UUCW)'!F10</f>
         <v>55</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <f aca="false">B10+B11</f>
         <v>60</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="8" t="n">
         <f aca="false">TCF!F19</f>
         <v>38.5</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <f aca="false">0.6+0.01*B13</f>
         <v>0.985</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="8" t="n">
         <f aca="false">ECF!F14</f>
         <v>15.5</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <f aca="false">1.4-0.03*B15</f>
         <v>0.935</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="8" t="n">
         <f aca="false">B12*B14*B16</f>
         <v>55.2585</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="10" t="n">
         <f aca="false">B17*B18</f>
         <v>1105.17</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="11" t="n">
-        <f aca="false">B19/4</f>
-        <v>276.2925</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="10" t="n">
+        <f aca="false">B19/3</f>
+        <v>368.39</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="10" t="n">
         <f aca="false">B20/B7</f>
-        <v>55.2585</v>
-      </c>
-      <c r="C21" s="8" t="s">
+        <v>73.678</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="7" t="str">
+      <c r="B22" s="6" t="str">
         <f aca="false">IF(B21&gt;60,"⚠ Acima do recomendado","✓ Dentro do esperado")</f>
-        <v>✓ Dentro do esperado</v>
-      </c>
-      <c r="C22" s="8" t="s">
+        <v>⚠ Acima do recomendado</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1597,203 +1593,203 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="7" t="n">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="6" t="n">
         <f aca="false">SUM(E5:E9)</f>
         <v>5</v>
       </c>
-      <c r="F10" s="18"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1822,222 +1818,222 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="13" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="15" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="13" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="15" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="7" t="n">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="6" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2066,441 +2062,441 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="26" t="n">
         <f aca="false">C5*D5</f>
         <v>4</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="30" t="n">
         <f aca="false">C6*D6</f>
         <v>4</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">C7*D7</f>
         <v>4</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="30" t="n">
         <f aca="false">C8*D8</f>
         <v>5</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">C9*D9</f>
         <v>3</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="22" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="30" t="n">
         <f aca="false">C10*D10</f>
         <v>1.5</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="28" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">C11*D11</f>
         <v>2</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="22" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="30" t="n">
         <f aca="false">C12*D12</f>
         <v>6</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">C13*D13</f>
         <v>3</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="22" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="30" t="n">
         <f aca="false">C14*D14</f>
         <v>3</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="28" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="26" t="n">
         <f aca="false">C15*D15</f>
         <v>1</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="22" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="30" t="n">
         <f aca="false">C16*D16</f>
         <v>1</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="28" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">C17*D17</f>
         <v>1</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="11" t="n">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="10" t="n">
         <f aca="false">SUM(E5:E17)</f>
         <v>38.5</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <f aca="false">E19</f>
         <v>38.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="9" t="n">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="8" t="n">
         <f aca="false">0.6+0.01*E19</f>
         <v>0.985</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="22" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="n">
+      <c r="A24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2533,297 +2529,297 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="26" t="n">
         <f aca="false">C5*D5</f>
         <v>3</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">C6*D6</f>
         <v>1</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="22" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">C7*D7</f>
         <v>3</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">C8*D8</f>
         <v>1.5</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="22" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">C9*D9</f>
         <v>4</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="22" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">C10*D10</f>
         <v>8</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="22" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="26" t="n">
         <v>-1</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">C11*D11</f>
         <v>-3</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="22" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="26" t="n">
         <v>-1</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">C12*D12</f>
         <v>-2</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="22" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="11" t="n">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="10" t="n">
         <f aca="false">SUM(E5:E12)</f>
         <v>15.5</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">E14</f>
         <v>15.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="9" t="n">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="8" t="n">
         <f aca="false">1.4-0.03*E14</f>
         <v>0.935</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="22" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2854,370 +2850,370 @@
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="32" t="n">
         <f aca="false">'Casos de Uso (UUCW)'!F5</f>
         <v>10</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="33" t="n">
         <f aca="false">C5/SUM($C$5:$C$8)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="24" t="n">
         <f aca="false">D5*Resumo!B19</f>
         <v>200.94</v>
       </c>
-      <c r="F5" s="25" t="n">
-        <f aca="false">E5/4</f>
-        <v>50.235</v>
+      <c r="F5" s="24" t="n">
+        <f aca="false">E5/3</f>
+        <v>66.98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="34" t="n">
         <f aca="false">'Casos de Uso (UUCW)'!F6</f>
         <v>15</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="35" t="n">
         <f aca="false">C6/SUM($C$5:$C$8)</f>
         <v>0.272727272727273</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="29" t="n">
         <f aca="false">D6*Resumo!B19</f>
         <v>301.41</v>
       </c>
-      <c r="F6" s="30" t="n">
-        <f aca="false">E6/4</f>
-        <v>75.3525</v>
+      <c r="F6" s="29" t="n">
+        <f aca="false">E6/3</f>
+        <v>100.47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="32" t="n">
         <f aca="false">'Casos de Uso (UUCW)'!F7</f>
         <v>15</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">C7/SUM($C$5:$C$8)</f>
         <v>0.272727272727273</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">D7*Resumo!B19</f>
         <v>301.41</v>
       </c>
-      <c r="F7" s="25" t="n">
-        <f aca="false">E7/4</f>
-        <v>75.3525</v>
+      <c r="F7" s="24" t="n">
+        <f aca="false">E7/3</f>
+        <v>100.47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="34" t="n">
         <f aca="false">'Casos de Uso (UUCW)'!F8</f>
         <v>15</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="35" t="n">
         <f aca="false">C8/SUM($C$5:$C$8)</f>
         <v>0.272727272727273</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <f aca="false">D8*Resumo!B19</f>
         <v>301.41</v>
       </c>
-      <c r="F8" s="30" t="n">
-        <f aca="false">E8/4</f>
-        <v>75.3525</v>
+      <c r="F8" s="29" t="n">
+        <f aca="false">E8/3</f>
+        <v>100.47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="37" t="n">
+      <c r="B9" s="16"/>
+      <c r="C9" s="36" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>55</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="37" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>1</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <f aca="false">SUM(E5:E8)</f>
         <v>1105.17</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>276.2925</v>
+        <v>368.39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="38" t="n">
         <v>0.05</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">C13*Resumo!B19</f>
         <v>55.2585</v>
       </c>
-      <c r="E13" s="27" t="n">
-        <f aca="false">D13/4</f>
-        <v>13.814625</v>
-      </c>
-      <c r="F13" s="23"/>
+      <c r="E13" s="26" t="n">
+        <f aca="false">D13/3</f>
+        <v>18.4195</v>
+      </c>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="38" t="n">
         <v>0.3</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="30" t="n">
         <f aca="false">C14*Resumo!B19</f>
         <v>331.551</v>
       </c>
-      <c r="E14" s="31" t="n">
-        <f aca="false">D14/4</f>
-        <v>82.88775</v>
-      </c>
-      <c r="F14" s="29"/>
+      <c r="E14" s="30" t="n">
+        <f aca="false">D14/3</f>
+        <v>110.517</v>
+      </c>
+      <c r="F14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="39" t="n">
+      <c r="C15" s="38" t="n">
         <v>0.3</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="26" t="n">
         <f aca="false">C15*Resumo!B19</f>
         <v>331.551</v>
       </c>
-      <c r="E15" s="27" t="n">
-        <f aca="false">D15/4</f>
-        <v>82.88775</v>
-      </c>
-      <c r="F15" s="23"/>
+      <c r="E15" s="26" t="n">
+        <f aca="false">D15/3</f>
+        <v>110.517</v>
+      </c>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="39" t="n">
+      <c r="C16" s="38" t="n">
         <v>0.2</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="30" t="n">
         <f aca="false">C16*Resumo!B19</f>
         <v>221.034</v>
       </c>
-      <c r="E16" s="31" t="n">
-        <f aca="false">D16/4</f>
-        <v>55.2585</v>
-      </c>
-      <c r="F16" s="29"/>
+      <c r="E16" s="30" t="n">
+        <f aca="false">D16/3</f>
+        <v>73.678</v>
+      </c>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C17" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">C17*Resumo!B19</f>
         <v>110.517</v>
       </c>
-      <c r="E17" s="27" t="n">
-        <f aca="false">D17/4</f>
-        <v>27.62925</v>
-      </c>
-      <c r="F17" s="23"/>
+      <c r="E17" s="26" t="n">
+        <f aca="false">D17/3</f>
+        <v>36.839</v>
+      </c>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C18" s="38" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="30" t="n">
         <f aca="false">C18*Resumo!B19</f>
         <v>55.2585</v>
       </c>
-      <c r="E18" s="31" t="n">
-        <f aca="false">D18/4</f>
-        <v>13.814625</v>
-      </c>
-      <c r="F18" s="29"/>
+      <c r="E18" s="30" t="n">
+        <f aca="false">D18/3</f>
+        <v>18.4195</v>
+      </c>
+      <c r="F18" s="28"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="38" t="n">
+      <c r="B19" s="16"/>
+      <c r="C19" s="37" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>1</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="10" t="n">
         <f aca="false">SUM(D13:D18)</f>
         <v>1105.17</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="10" t="n">
         <f aca="false">SUM(E13:E18)</f>
-        <v>276.2925</v>
+        <v>368.39</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="8">
